--- a/relatorio_ph_lotes.xlsx
+++ b/relatorio_ph_lotes.xlsx
@@ -397,16 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:E158"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,1226 +411,2690 @@
         <v>Lote</v>
       </c>
       <c r="B1" t="str">
-        <v>Tipo</v>
+        <v>Queijo</v>
       </c>
       <c r="C1" t="str">
-        <v>ID</v>
+        <v>Nº Medição</v>
       </c>
       <c r="D1" t="str">
-        <v>Início (BRT)</v>
+        <v>Hora da Medição</v>
       </c>
       <c r="E1" t="str">
-        <v>Conclusão (BRT)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Nº Medição</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Hora da Medição (BRT)</v>
-      </c>
-      <c r="H1" t="str">
         <v>pH</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>070126</v>
+        <v>190226</v>
       </c>
       <c r="B2" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>07/01/2026, 16:00:57</v>
-      </c>
-      <c r="E2" t="str">
-        <v>07/01/2026, 16:12:43</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v>07/01/2026, 16:06:21</v>
-      </c>
-      <c r="H2">
-        <v>6.48</v>
+        <v>19/02/2026 11:31</v>
+      </c>
+      <c r="E2">
+        <v>6.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>070126</v>
+        <v>190226</v>
       </c>
       <c r="B3" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>07/01/2026, 16:00:57</v>
-      </c>
-      <c r="E3" t="str">
-        <v>07/01/2026, 16:12:43</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="str">
-        <v>07/01/2026, 16:07:15</v>
-      </c>
-      <c r="H3">
-        <v>5.8</v>
+        <v>19/02/2026 13:01</v>
+      </c>
+      <c r="E3">
+        <v>5.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>070126</v>
+        <v>190226</v>
       </c>
       <c r="B4" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>07/01/2026, 16:00:57</v>
-      </c>
-      <c r="E4" t="str">
-        <v>07/01/2026, 16:12:43</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="str">
-        <v>07/01/2026, 16:07:31</v>
-      </c>
-      <c r="H4">
-        <v>5.29</v>
+        <v>19/02/2026 13:01</v>
+      </c>
+      <c r="E4">
+        <v>5.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>070126</v>
+        <v>200226</v>
       </c>
       <c r="B5" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>07/01/2026, 16:00:57</v>
-      </c>
-      <c r="E5" t="str">
-        <v>07/01/2026, 16:12:43</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="str">
-        <v>07/01/2026, 16:08:16</v>
-      </c>
-      <c r="H5">
-        <v>5.2</v>
+        <v>20/02/2026 11:04</v>
+      </c>
+      <c r="E5">
+        <v>6.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>070126</v>
+        <v>200226</v>
       </c>
       <c r="B6" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D6" t="str">
-        <v>07/01/2026, 17:26:05</v>
-      </c>
-      <c r="E6" t="str">
-        <v>07/01/2026, 17:39:06</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="str">
-        <v>07/01/2026, 17:35:59</v>
-      </c>
-      <c r="H6">
-        <v>6.5</v>
+        <v>20/02/2026 12:55</v>
+      </c>
+      <c r="E6">
+        <v>5.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>070126</v>
+        <v>200226</v>
       </c>
       <c r="B7" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D7" t="str">
-        <v>07/01/2026, 17:26:05</v>
-      </c>
-      <c r="E7" t="str">
-        <v>07/01/2026, 17:39:06</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" t="str">
-        <v>07/01/2026, 17:36:35</v>
-      </c>
-      <c r="H7">
-        <v>5.3</v>
+        <v>20/02/2026 14:09</v>
+      </c>
+      <c r="E7">
+        <v>5.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>070126</v>
+        <v>240226</v>
       </c>
       <c r="B8" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C8">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>07/01/2026, 17:26:05</v>
-      </c>
-      <c r="E8" t="str">
-        <v>07/01/2026, 17:39:06</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8" t="str">
-        <v>07/01/2026, 17:36:43</v>
-      </c>
-      <c r="H8">
-        <v>5.29</v>
+        <v>24/02/2026 11:36</v>
+      </c>
+      <c r="E8">
+        <v>6.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>070126</v>
+        <v>240226</v>
       </c>
       <c r="B9" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D9" t="str">
-        <v>07/01/2026, 17:26:05</v>
-      </c>
-      <c r="E9" t="str">
-        <v>07/01/2026, 17:39:06</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9" t="str">
-        <v>07/01/2026, 17:36:51</v>
-      </c>
-      <c r="H9">
-        <v>5.2</v>
+        <v>24/02/2026 13:16</v>
+      </c>
+      <c r="E9">
+        <v>6.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>080126</v>
+        <v>240226</v>
       </c>
       <c r="B10" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D10" t="str">
-        <v>08/01/2026, 22:03:30</v>
-      </c>
-      <c r="E10" t="str">
-        <v>13/01/2026, 22:39:15</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>13/01/2026, 22:35:03</v>
-      </c>
-      <c r="H10">
-        <v>5.6</v>
+        <v>24/02/2026 14:39</v>
+      </c>
+      <c r="E10">
+        <v>5.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>080126</v>
+        <v>240226</v>
       </c>
       <c r="B11" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D11" t="str">
-        <v>08/01/2026, 22:03:30</v>
-      </c>
-      <c r="E11" t="str">
-        <v>13/01/2026, 22:39:15</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11" t="str">
-        <v>13/01/2026, 22:35:32</v>
-      </c>
-      <c r="H11">
-        <v>5.5</v>
+        <v>24/02/2026 15:31</v>
+      </c>
+      <c r="E11">
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>080126</v>
+        <v>270226</v>
       </c>
       <c r="B12" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D12" t="str">
-        <v>08/01/2026, 22:03:30</v>
-      </c>
-      <c r="E12" t="str">
-        <v>13/01/2026, 22:39:15</v>
-      </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12" t="str">
-        <v>13/01/2026, 22:35:49</v>
-      </c>
-      <c r="H12">
-        <v>5.3</v>
+        <v>27/02/2026 10:57</v>
+      </c>
+      <c r="E12">
+        <v>6.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>080126</v>
+        <v>270226</v>
       </c>
       <c r="B13" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D13" t="str">
-        <v>08/01/2026, 22:03:30</v>
-      </c>
-      <c r="E13" t="str">
-        <v>13/01/2026, 22:39:15</v>
-      </c>
-      <c r="F13">
-        <v>4</v>
-      </c>
-      <c r="G13" t="str">
-        <v>13/01/2026, 22:36:07</v>
-      </c>
-      <c r="H13">
-        <v>5.2</v>
+        <v>27/02/2026 13:17</v>
+      </c>
+      <c r="E13">
+        <v>5.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>280126</v>
+        <v>270226</v>
       </c>
       <c r="B14" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C14">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
-        <v>28/01/2026, 21:32:39</v>
-      </c>
-      <c r="E14" t="str">
-        <v>30/01/2026, 23:08:03</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="str">
-        <v>30/01/2026, 21:26:16</v>
-      </c>
-      <c r="H14">
-        <v>5.2</v>
+        <v>27/02/2026 14:32</v>
+      </c>
+      <c r="E14">
+        <v>5.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>050226</v>
+        <v>270226</v>
       </c>
       <c r="B15" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D15" t="str">
-        <v>05/02/2026, 21:20:45</v>
-      </c>
-      <c r="E15" t="str">
-        <v>05/02/2026, 21:32:02</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="str">
-        <v>05/02/2026, 21:28:56</v>
-      </c>
-      <c r="H15">
-        <v>5.4</v>
+        <v>27/02/2026 15:01</v>
+      </c>
+      <c r="E15">
+        <v>5.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>050226</v>
+        <v>280226</v>
       </c>
       <c r="B16" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C16">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D16" t="str">
-        <v>05/02/2026, 21:20:45</v>
-      </c>
-      <c r="E16" t="str">
-        <v>05/02/2026, 21:32:02</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" t="str">
-        <v>05/02/2026, 21:29:09</v>
-      </c>
-      <c r="H16">
-        <v>5.3</v>
+        <v>28/02/2026 11:33</v>
+      </c>
+      <c r="E16">
+        <v>6.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>050226</v>
+        <v>280226</v>
       </c>
       <c r="B17" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C17">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
-        <v>05/02/2026, 21:20:45</v>
-      </c>
-      <c r="E17" t="str">
-        <v>05/02/2026, 21:32:02</v>
-      </c>
-      <c r="F17">
-        <v>3</v>
-      </c>
-      <c r="G17" t="str">
-        <v>05/02/2026, 21:29:23</v>
-      </c>
-      <c r="H17">
-        <v>5.2</v>
+        <v>28/02/2026 13:14</v>
+      </c>
+      <c r="E17">
+        <v>5.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>050226</v>
+        <v>280226</v>
       </c>
       <c r="B18" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C18">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D18" t="str">
-        <v>05/02/2026, 21:59:53</v>
-      </c>
-      <c r="E18" t="str">
-        <v>12/02/2026, 21:41:21</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="str">
-        <v>12/02/2026, 21:38:07</v>
-      </c>
-      <c r="H18">
-        <v>5.2</v>
+        <v>28/02/2026 14:48</v>
+      </c>
+      <c r="E18">
+        <v>5.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>050226</v>
+        <v>280226</v>
       </c>
       <c r="B19" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C19">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D19" t="str">
-        <v>05/02/2026, 22:02:10</v>
-      </c>
-      <c r="E19" t="str">
-        <v>05/02/2026, 22:30:20</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="str">
-        <v>05/02/2026, 22:27:07</v>
-      </c>
-      <c r="H19">
-        <v>5.6</v>
+        <v>28/02/2026 15:11</v>
+      </c>
+      <c r="E19">
+        <v>5.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>050226</v>
+        <v>030326</v>
       </c>
       <c r="B20" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C20">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D20" t="str">
-        <v>05/02/2026, 22:02:10</v>
-      </c>
-      <c r="E20" t="str">
-        <v>05/02/2026, 22:30:20</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20" t="str">
-        <v>05/02/2026, 22:27:23</v>
-      </c>
-      <c r="H20">
-        <v>5.2</v>
+        <v>03/03/2026 10:49</v>
+      </c>
+      <c r="E20">
+        <v>6.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>190226</v>
+        <v>030326</v>
       </c>
       <c r="B21" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C21">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
-        <v>19/02/2026, 08:23:38</v>
-      </c>
-      <c r="E21" t="str">
-        <v>25/02/2026, 22:27:03</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="str">
-        <v>19/02/2026, 11:31:43</v>
-      </c>
-      <c r="H21">
-        <v>6.18</v>
+        <v>03/03/2026 12:40</v>
+      </c>
+      <c r="E21">
+        <v>5.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>190226</v>
+        <v>030326</v>
       </c>
       <c r="B22" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C22">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D22" t="str">
-        <v>19/02/2026, 08:23:38</v>
-      </c>
-      <c r="E22" t="str">
-        <v>25/02/2026, 22:27:03</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22" t="str">
-        <v>19/02/2026, 13:01:21</v>
-      </c>
-      <c r="H22">
-        <v>5.49</v>
+        <v>03/03/2026 14:13</v>
+      </c>
+      <c r="E22">
+        <v>5.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>190226</v>
+        <v>030326</v>
       </c>
       <c r="B23" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C23">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="D23" t="str">
-        <v>19/02/2026, 08:23:38</v>
-      </c>
-      <c r="E23" t="str">
-        <v>25/02/2026, 22:27:03</v>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23" t="str">
-        <v>19/02/2026, 13:01:46</v>
-      </c>
-      <c r="H23">
-        <v>5.49</v>
+        <v>03/03/2026 15:01</v>
+      </c>
+      <c r="E23">
+        <v>5.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>190226</v>
+        <v>060326</v>
       </c>
       <c r="B24" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C24">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>19/02/2026, 23:35:37</v>
-      </c>
-      <c r="E24" t="str">
-        <v>20/05/2026, 21:49:53</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="str">
-        <v>20/05/2026, 21:46:25</v>
-      </c>
-      <c r="H24">
-        <v>5.2</v>
+        <v>06/03/2026 11:09</v>
+      </c>
+      <c r="E24">
+        <v>6.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>190226</v>
+        <v>060326</v>
       </c>
       <c r="B25" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C25">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="D25" t="str">
-        <v>19/02/2026, 23:47:38</v>
-      </c>
-      <c r="E25" t="str">
-        <v>14/07/2026, 15:17:30</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="str">
-        <v>20/03/2026, 21:47:54</v>
-      </c>
-      <c r="H25">
-        <v>6.1</v>
+        <v>06/03/2026 12:56</v>
+      </c>
+      <c r="E25">
+        <v>5.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>190226</v>
+        <v>060326</v>
       </c>
       <c r="B26" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C26">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D26" t="str">
-        <v>19/02/2026, 23:47:38</v>
-      </c>
-      <c r="E26" t="str">
-        <v>14/07/2026, 15:17:30</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26" t="str">
-        <v>20/05/2026, 23:07:06</v>
-      </c>
-      <c r="H26">
-        <v>6</v>
+        <v>06/03/2026 14:06</v>
+      </c>
+      <c r="E26">
+        <v>5.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>190226</v>
+        <v>070326</v>
       </c>
       <c r="B27" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C27">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D27" t="str">
-        <v>19/02/2026, 23:47:38</v>
-      </c>
-      <c r="E27" t="str">
-        <v>14/07/2026, 15:17:30</v>
-      </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="G27" t="str">
-        <v>20/05/2026, 23:07:13</v>
-      </c>
-      <c r="H27">
-        <v>5.2</v>
+        <v>07/03/2026 11:56</v>
+      </c>
+      <c r="E27">
+        <v>6.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>190226</v>
+        <v>070326</v>
       </c>
       <c r="B28" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C28">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D28" t="str">
-        <v>19/02/2026, 23:50:06</v>
-      </c>
-      <c r="E28" t="str">
-        <v>25/02/2026, 22:54:45</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="str">
-        <v>20/02/2026, 12:34:34</v>
-      </c>
-      <c r="H28">
-        <v>5.7</v>
+        <v>07/03/2026 13:34</v>
+      </c>
+      <c r="E28">
+        <v>6.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>190226</v>
+        <v>070326</v>
       </c>
       <c r="B29" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C29">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D29" t="str">
-        <v>19/02/2026, 23:50:06</v>
-      </c>
-      <c r="E29" t="str">
-        <v>25/02/2026, 22:54:45</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
-      </c>
-      <c r="G29" t="str">
-        <v>20/02/2026, 12:39:45</v>
-      </c>
-      <c r="H29">
-        <v>5.8</v>
+        <v>07/03/2026 15:14</v>
+      </c>
+      <c r="E29">
+        <v>5.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>190226</v>
+        <v>100326</v>
       </c>
       <c r="B30" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C30">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D30" t="str">
-        <v>19/02/2026, 23:50:06</v>
-      </c>
-      <c r="E30" t="str">
-        <v>25/02/2026, 22:54:45</v>
-      </c>
-      <c r="F30">
-        <v>3</v>
-      </c>
-      <c r="G30" t="str">
-        <v>20/02/2026, 12:42:22</v>
-      </c>
-      <c r="H30">
-        <v>5.6</v>
+        <v>10/03/2026 11:44</v>
+      </c>
+      <c r="E30">
+        <v>6.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>190226</v>
+        <v>100326</v>
       </c>
       <c r="B31" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C31">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D31" t="str">
-        <v>19/02/2026, 23:50:06</v>
-      </c>
-      <c r="E31" t="str">
-        <v>25/02/2026, 22:54:45</v>
-      </c>
-      <c r="F31">
-        <v>4</v>
-      </c>
-      <c r="G31" t="str">
-        <v>20/02/2026, 12:42:33</v>
-      </c>
-      <c r="H31">
-        <v>5.5</v>
+        <v>10/03/2026 13:38</v>
+      </c>
+      <c r="E31">
+        <v>5.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>190226</v>
+        <v>130326</v>
       </c>
       <c r="B32" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C32">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D32" t="str">
-        <v>19/02/2026, 23:50:06</v>
-      </c>
-      <c r="E32" t="str">
-        <v>25/02/2026, 22:54:45</v>
-      </c>
-      <c r="F32">
-        <v>5</v>
-      </c>
-      <c r="G32" t="str">
-        <v>20/02/2026, 12:42:47</v>
-      </c>
-      <c r="H32">
-        <v>5.3</v>
+        <v>13/03/2026 11:09</v>
+      </c>
+      <c r="E32">
+        <v>6.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>190226</v>
+        <v>130326</v>
       </c>
       <c r="B33" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C33">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D33" t="str">
-        <v>19/02/2026, 23:50:06</v>
-      </c>
-      <c r="E33" t="str">
-        <v>25/02/2026, 22:54:45</v>
-      </c>
-      <c r="F33">
-        <v>6</v>
-      </c>
-      <c r="G33" t="str">
-        <v>20/02/2026, 12:42:55</v>
-      </c>
-      <c r="H33">
-        <v>5.295</v>
+        <v>13/03/2026 13:07</v>
+      </c>
+      <c r="E33">
+        <v>5.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>250226</v>
+        <v>130326</v>
       </c>
       <c r="B34" t="str">
         <v>Queijo Nete</v>
       </c>
       <c r="C34">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D34" t="str">
-        <v>25/02/2026, 22:22:30</v>
-      </c>
-      <c r="E34" t="str">
-        <v>26/03/2026, 22:15:21</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" t="str">
-        <v>06/03/2026, 00:16:53</v>
-      </c>
-      <c r="H34">
+        <v>13/03/2026 14:13</v>
+      </c>
+      <c r="E34">
         <v>5.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>140726</v>
+        <v>170326</v>
       </c>
       <c r="B35" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C35">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D35" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E35" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" t="str">
-        <v>14/07/2026, 18:45:48</v>
-      </c>
-      <c r="H35">
-        <v>5.8</v>
+        <v>17/03/2026 10:58</v>
+      </c>
+      <c r="E35">
+        <v>6.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>140726</v>
+        <v>170326</v>
       </c>
       <c r="B36" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C36">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D36" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E36" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36" t="str">
-        <v>14/07/2026, 18:46:32</v>
-      </c>
-      <c r="H36">
-        <v>5.7</v>
+        <v>17/03/2026 13:02</v>
+      </c>
+      <c r="E36">
+        <v>5.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>140726</v>
+        <v>200326</v>
       </c>
       <c r="B37" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C37">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D37" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E37" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37" t="str">
-        <v>14/07/2026, 18:46:54</v>
-      </c>
-      <c r="H37">
-        <v>5.6</v>
+        <v>20/03/2026 11:44</v>
+      </c>
+      <c r="E37">
+        <v>5.81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>140726</v>
+        <v>200326</v>
       </c>
       <c r="B38" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C38">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D38" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E38" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F38">
-        <v>4</v>
-      </c>
-      <c r="G38" t="str">
-        <v>14/07/2026, 18:56:52</v>
-      </c>
-      <c r="H38">
-        <v>5.5</v>
+        <v>20/03/2026 13:10</v>
+      </c>
+      <c r="E38">
+        <v>5.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>140726</v>
+        <v>250326</v>
       </c>
       <c r="B39" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C39">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D39" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E39" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F39">
-        <v>5</v>
-      </c>
-      <c r="G39" t="str">
-        <v>14/07/2026, 18:57:07</v>
-      </c>
-      <c r="H39">
-        <v>5.4</v>
+        <v>25/03/2026 11:41</v>
+      </c>
+      <c r="E39">
+        <v>6.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>140726</v>
+        <v>250326</v>
       </c>
       <c r="B40" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C40">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D40" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E40" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F40">
-        <v>6</v>
-      </c>
-      <c r="G40" t="str">
-        <v>14/07/2026, 19:23:21</v>
-      </c>
-      <c r="H40">
-        <v>5.35</v>
+        <v>25/03/2026 13:30</v>
+      </c>
+      <c r="E40">
+        <v>5.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>140726</v>
+        <v>250326</v>
       </c>
       <c r="B41" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C41">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D41" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E41" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F41">
-        <v>7</v>
-      </c>
-      <c r="G41" t="str">
-        <v>14/07/2026, 19:25:22</v>
-      </c>
-      <c r="H41">
-        <v>5.34</v>
+        <v>27/03/2026 06:32</v>
+      </c>
+      <c r="E41">
+        <v>5.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>140726</v>
+        <v>280326</v>
       </c>
       <c r="B42" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C42">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D42" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E42" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="G42" t="str">
-        <v>14/07/2026, 19:25:38</v>
-      </c>
-      <c r="H42">
-        <v>5.3</v>
+        <v>28/03/2026 11:07</v>
+      </c>
+      <c r="E42">
+        <v>6.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>140726</v>
+        <v>280326</v>
       </c>
       <c r="B43" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C43">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D43" t="str">
-        <v>14/07/2026, 14:55:47</v>
-      </c>
-      <c r="E43" t="str">
-        <v>14/07/2026, 19:26:35</v>
-      </c>
-      <c r="F43">
-        <v>9</v>
-      </c>
-      <c r="G43" t="str">
-        <v>14/07/2026, 19:25:50</v>
-      </c>
-      <c r="H43">
-        <v>5.29</v>
+        <v>28/03/2026 12:38</v>
+      </c>
+      <c r="E43">
+        <v>6.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>150726</v>
+        <v>280326</v>
       </c>
       <c r="B44" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C44">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D44" t="str">
-        <v>15/07/2026, 11:11:46</v>
-      </c>
-      <c r="E44" t="str">
-        <v>17/07/2026, 00:14:19</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="str">
-        <v>16/07/2026, 23:20:48</v>
-      </c>
-      <c r="H44">
-        <v>5.4</v>
+        <v>28/03/2026 13:33</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>150726</v>
+        <v>280326</v>
       </c>
       <c r="B45" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C45">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="D45" t="str">
-        <v>15/07/2026, 11:11:46</v>
-      </c>
-      <c r="E45" t="str">
-        <v>17/07/2026, 00:14:19</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
-      </c>
-      <c r="G45" t="str">
-        <v>16/07/2026, 23:21:25</v>
-      </c>
-      <c r="H45">
-        <v>5.3</v>
+        <v>28/03/2026 15:06</v>
+      </c>
+      <c r="E45">
+        <v>5.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>150726</v>
+        <v>280326</v>
       </c>
       <c r="B46" t="str">
-        <v>Queijo Nina</v>
+        <v>Queijo Nete</v>
       </c>
       <c r="C46">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D46" t="str">
-        <v>15/07/2026, 11:11:46</v>
-      </c>
-      <c r="E46" t="str">
-        <v>17/07/2026, 00:14:19</v>
-      </c>
-      <c r="F46">
-        <v>3</v>
-      </c>
-      <c r="G46" t="str">
-        <v>16/07/2026, 23:22:28</v>
-      </c>
-      <c r="H46">
-        <v>5.26</v>
+        <v>28/03/2026 15:42</v>
+      </c>
+      <c r="E46">
+        <v>5.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>040426</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="str">
+        <v>04/04/2026 12:33</v>
+      </c>
+      <c r="E47">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>040426</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="str">
+        <v>04/04/2026 14:05</v>
+      </c>
+      <c r="E48">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>080426</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="str">
+        <v>08/04/2026 13:12</v>
+      </c>
+      <c r="E49">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>080426</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50" t="str">
+        <v>08/04/2026 14:44</v>
+      </c>
+      <c r="E50">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>080426</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="str">
+        <v>08/04/2026 16:21</v>
+      </c>
+      <c r="E51">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>110426</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="str">
+        <v>11/04/2026 11:32</v>
+      </c>
+      <c r="E52">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>110426</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="str">
+        <v>11/04/2026 13:27</v>
+      </c>
+      <c r="E53">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>110426</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="str">
+        <v>11/04/2026 15:56</v>
+      </c>
+      <c r="E54">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>110426</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="str">
+        <v>11/04/2026 16:56</v>
+      </c>
+      <c r="E55">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>170426</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="str">
+        <v>17/04/2026 12:05</v>
+      </c>
+      <c r="E56">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>170426</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="str">
+        <v>17/04/2026 13:55</v>
+      </c>
+      <c r="E57">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>170426</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="str">
+        <v>17/04/2026 17:35</v>
+      </c>
+      <c r="E58">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>180426</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="str">
+        <v>18/04/2026 12:16</v>
+      </c>
+      <c r="E59">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>180426</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="str">
+        <v>18/04/2026 14:00</v>
+      </c>
+      <c r="E60">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>180426</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="str">
+        <v>18/04/2026 15:36</v>
+      </c>
+      <c r="E61">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>220426</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="str">
+        <v>22/04/2026 11:58</v>
+      </c>
+      <c r="E62">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>220426</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="str">
+        <v>22/04/2026 14:01</v>
+      </c>
+      <c r="E63">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>220426</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="str">
+        <v>22/04/2026 21:17</v>
+      </c>
+      <c r="E64">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>230426</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="str">
+        <v>23/04/2026 13:40</v>
+      </c>
+      <c r="E65">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>230426</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66" t="str">
+        <v>23/04/2026 16:11</v>
+      </c>
+      <c r="E66">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>250426</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67" t="str">
+        <v>25/04/2026 11:48</v>
+      </c>
+      <c r="E67">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>250426</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68" t="str">
+        <v>25/04/2026 14:26</v>
+      </c>
+      <c r="E68">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>250426</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="str">
+        <v>25/04/2026 16:56</v>
+      </c>
+      <c r="E69">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>300426</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="str">
+        <v>30/04/2026 10:29</v>
+      </c>
+      <c r="E70">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>300426</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71" t="str">
+        <v>30/04/2026 12:31</v>
+      </c>
+      <c r="E71">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>300426</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="str">
+        <v>30/04/2026 13:44</v>
+      </c>
+      <c r="E72">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>020526</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="str">
+        <v>02/05/2026 13:55</v>
+      </c>
+      <c r="E73">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>020526</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74" t="str">
+        <v>02/05/2026 14:39</v>
+      </c>
+      <c r="E74">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>050526</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75" t="str">
+        <v>05/05/2026 11:50</v>
+      </c>
+      <c r="E75">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>050526</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76" t="str">
+        <v>05/05/2026 14:11</v>
+      </c>
+      <c r="E76">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>080526</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="str">
+        <v>08/05/2026 13:02</v>
+      </c>
+      <c r="E77">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>080526</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="str">
+        <v>08/05/2026 14:45</v>
+      </c>
+      <c r="E78">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>090526</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="str">
+        <v>09/05/2026 12:50</v>
+      </c>
+      <c r="E79">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>090526</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80" t="str">
+        <v>09/05/2026 14:43</v>
+      </c>
+      <c r="E80">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>120526</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="str">
+        <v>13/05/2026 06:15</v>
+      </c>
+      <c r="E81">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>120526</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82" t="str">
+        <v>13/05/2026 06:16</v>
+      </c>
+      <c r="E82">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>120526</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="str">
+        <v>13/05/2026 06:16</v>
+      </c>
+      <c r="E83">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>150526</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="str">
+        <v>15/05/2026 11:36</v>
+      </c>
+      <c r="E84">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>150526</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85" t="str">
+        <v>15/05/2026 13:12</v>
+      </c>
+      <c r="E85">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>150526</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86" t="str">
+        <v>15/05/2026 14:16</v>
+      </c>
+      <c r="E86">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>150526</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C87">
+        <v>4</v>
+      </c>
+      <c r="D87" t="str">
+        <v>16/05/2026 06:09</v>
+      </c>
+      <c r="E87">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>160526</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="str">
+        <v>16/05/2026 11:47</v>
+      </c>
+      <c r="E88">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>160526</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89" t="str">
+        <v>16/05/2026 14:08</v>
+      </c>
+      <c r="E89">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>160526</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" t="str">
+        <v>16/05/2026 14:39</v>
+      </c>
+      <c r="E90">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>190526</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="str">
+        <v>19/05/2026 11:33</v>
+      </c>
+      <c r="E91">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>190526</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92" t="str">
+        <v>19/05/2026 13:52</v>
+      </c>
+      <c r="E92">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>190526</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93" t="str">
+        <v>19/05/2026 15:16</v>
+      </c>
+      <c r="E93">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>190526</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C94">
+        <v>4</v>
+      </c>
+      <c r="D94" t="str">
+        <v>20/05/2026 06:31</v>
+      </c>
+      <c r="E94">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>220526</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="str">
+        <v>22/05/2026 13:06</v>
+      </c>
+      <c r="E95">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>220526</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="str">
+        <v>22/05/2026 13:57</v>
+      </c>
+      <c r="E96">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>220526</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C97">
+        <v>3</v>
+      </c>
+      <c r="D97" t="str">
+        <v>25/05/2026 06:33</v>
+      </c>
+      <c r="E97">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>260526</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="str">
+        <v>26/05/2026 13:08</v>
+      </c>
+      <c r="E98">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>260526</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="str">
+        <v>26/05/2026 14:44</v>
+      </c>
+      <c r="E99">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>260526</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="str">
+        <v>26/05/2026 15:40</v>
+      </c>
+      <c r="E100">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>260526</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101" t="str">
+        <v>26/05/2026 17:14</v>
+      </c>
+      <c r="E101">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>260526</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C102">
+        <v>5</v>
+      </c>
+      <c r="D102" t="str">
+        <v>26/05/2026 17:16</v>
+      </c>
+      <c r="E102">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>260526</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C103">
+        <v>6</v>
+      </c>
+      <c r="D103" t="str">
+        <v>27/05/2026 06:32</v>
+      </c>
+      <c r="E103">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>290526</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="str">
+        <v>29/05/2026 11:29</v>
+      </c>
+      <c r="E104">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>290526</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="str">
+        <v>29/05/2026 13:01</v>
+      </c>
+      <c r="E105">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>290526</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="str">
+        <v>29/05/2026 13:44</v>
+      </c>
+      <c r="E106">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>290526</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="D107" t="str">
+        <v>30/05/2026 06:51</v>
+      </c>
+      <c r="E107">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>300526</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108" t="str">
+        <v>30/05/2026 11:47</v>
+      </c>
+      <c r="E108">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>300526</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+      <c r="D109" t="str">
+        <v>30/05/2026 14:10</v>
+      </c>
+      <c r="E109">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>030626</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="str">
+        <v>03/06/2026 14:02</v>
+      </c>
+      <c r="E110">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>030626</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="str">
+        <v>03/06/2026 15:33</v>
+      </c>
+      <c r="E111">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>090626</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="str">
+        <v>09/06/2026 13:37</v>
+      </c>
+      <c r="E112">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>090626</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113" t="str">
+        <v>09/06/2026 14:45</v>
+      </c>
+      <c r="E113">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>090626</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+      <c r="D114" t="str">
+        <v>10/06/2026 06:43</v>
+      </c>
+      <c r="E114">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>120626</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115" t="str">
+        <v>12/06/2026 14:10</v>
+      </c>
+      <c r="E115">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>120626</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="str">
+        <v>12/06/2026 14:11</v>
+      </c>
+      <c r="E116">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>120626</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
+      </c>
+      <c r="D117" t="str">
+        <v>15/06/2026 07:21</v>
+      </c>
+      <c r="E117">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>160626</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="str">
+        <v>16/06/2026 11:51</v>
+      </c>
+      <c r="E118">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>160626</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C119">
+        <v>2</v>
+      </c>
+      <c r="D119" t="str">
+        <v>16/06/2026 14:17</v>
+      </c>
+      <c r="E119">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>160626</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C120">
+        <v>3</v>
+      </c>
+      <c r="D120" t="str">
+        <v>16/06/2026 15:24</v>
+      </c>
+      <c r="E120">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>160626</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C121">
+        <v>4</v>
+      </c>
+      <c r="D121" t="str">
+        <v>17/06/2026 06:34</v>
+      </c>
+      <c r="E121">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>190626</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="str">
+        <v>19/06/2026 10:45</v>
+      </c>
+      <c r="E122">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>190626</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="str">
+        <v>19/06/2026 14:21</v>
+      </c>
+      <c r="E123">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>190626</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="str">
+        <v>19/06/2026 14:21</v>
+      </c>
+      <c r="E124">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>190626</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125" t="str">
+        <v>19/06/2026 18:08</v>
+      </c>
+      <c r="E125">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>200626</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126" t="str">
+        <v>20/06/2026 11:09</v>
+      </c>
+      <c r="E126">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>200626</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+      <c r="D127" t="str">
+        <v>20/06/2026 13:11</v>
+      </c>
+      <c r="E127">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>200626</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C128">
+        <v>3</v>
+      </c>
+      <c r="D128" t="str">
+        <v>20/06/2026 13:58</v>
+      </c>
+      <c r="E128">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>230626</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129" t="str">
+        <v>23/06/2026 12:28</v>
+      </c>
+      <c r="E129">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>230626</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+      <c r="D130" t="str">
+        <v>23/06/2026 14:06</v>
+      </c>
+      <c r="E130">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>230626</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C131">
+        <v>3</v>
+      </c>
+      <c r="D131" t="str">
+        <v>23/06/2026 15:46</v>
+      </c>
+      <c r="E131">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>260626</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132" t="str">
+        <v>26/06/2026 12:32</v>
+      </c>
+      <c r="E132">
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>260626</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133" t="str">
+        <v>26/06/2026 13:52</v>
+      </c>
+      <c r="E133">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>260626</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134" t="str">
+        <v>27/06/2026 06:29</v>
+      </c>
+      <c r="E134">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>270626</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="str">
+        <v>27/06/2026 13:48</v>
+      </c>
+      <c r="E135">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>270626</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="D136" t="str">
+        <v>29/06/2026 06:39</v>
+      </c>
+      <c r="E136">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>300626</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="str">
+        <v>30/06/2026 11:40</v>
+      </c>
+      <c r="E137">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>300626</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138" t="str">
+        <v>30/06/2026 14:10</v>
+      </c>
+      <c r="E138">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>030726</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139" t="str">
+        <v>03/07/2026 11:32</v>
+      </c>
+      <c r="E139">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>030726</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140" t="str">
+        <v>03/07/2026 14:13</v>
+      </c>
+      <c r="E140">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>030726</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C141">
+        <v>3</v>
+      </c>
+      <c r="D141" t="str">
+        <v>06/07/2026 06:40</v>
+      </c>
+      <c r="E141">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>070726</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142" t="str">
+        <v>08/07/2026 06:36</v>
+      </c>
+      <c r="E142">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>100726</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="str">
+        <v>10/07/2026 10:54</v>
+      </c>
+      <c r="E143">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>100726</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144" t="str">
+        <v>10/07/2026 13:18</v>
+      </c>
+      <c r="E144">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>100726</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C145">
+        <v>3</v>
+      </c>
+      <c r="D145" t="str">
+        <v>10/07/2026 14:04</v>
+      </c>
+      <c r="E145">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>110726</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" t="str">
+        <v>11/07/2026 14:23</v>
+      </c>
+      <c r="E146">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>110726</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C147">
+        <v>2</v>
+      </c>
+      <c r="D147" t="str">
+        <v>11/07/2026 14:23</v>
+      </c>
+      <c r="E147">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>110726</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C148">
+        <v>3</v>
+      </c>
+      <c r="D148" t="str">
+        <v>13/07/2026 06:41</v>
+      </c>
+      <c r="E148">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>140726</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="str">
+        <v>14/07/2026 11:31</v>
+      </c>
+      <c r="E149">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>140726</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+      <c r="D150" t="str">
+        <v>14/07/2026 12:53</v>
+      </c>
+      <c r="E150">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>140726</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C151">
+        <v>3</v>
+      </c>
+      <c r="D151" t="str">
+        <v>14/07/2026 12:54</v>
+      </c>
+      <c r="E151">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>140726</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C152">
+        <v>4</v>
+      </c>
+      <c r="D152" t="str">
+        <v>15/07/2026 06:39</v>
+      </c>
+      <c r="E152">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>140726</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C153">
+        <v>5</v>
+      </c>
+      <c r="D153" t="str">
+        <v>15/07/2026 06:40</v>
+      </c>
+      <c r="E153">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
         <v>150726</v>
       </c>
-      <c r="B47" t="str">
+      <c r="B154" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154" t="str">
+        <v>15/07/2026 14:57</v>
+      </c>
+      <c r="E154">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>150726</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Queijo Nete</v>
+      </c>
+      <c r="C155">
+        <v>2</v>
+      </c>
+      <c r="D155" t="str">
+        <v>15/07/2026 14:57</v>
+      </c>
+      <c r="E155">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>170726</v>
+      </c>
+      <c r="B156" t="str">
         <v>Queijo Nina</v>
       </c>
-      <c r="C47">
-        <v>62</v>
-      </c>
-      <c r="D47" t="str">
-        <v>15/07/2026, 11:11:46</v>
-      </c>
-      <c r="E47" t="str">
-        <v>17/07/2026, 00:14:19</v>
-      </c>
-      <c r="F47">
-        <v>4</v>
-      </c>
-      <c r="G47" t="str">
-        <v>20/07/2026, 13:41:56</v>
-      </c>
-      <c r="H47">
-        <v>5.2</v>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156" t="str">
+        <v>17/07/2026 14:12</v>
+      </c>
+      <c r="E156">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>170726</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Queijo Nina</v>
+      </c>
+      <c r="C157">
+        <v>2</v>
+      </c>
+      <c r="D157" t="str">
+        <v>20/07/2026 14:12</v>
+      </c>
+      <c r="E157">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>170726</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Queijo Nina</v>
+      </c>
+      <c r="C158">
+        <v>3</v>
+      </c>
+      <c r="D158" t="str">
+        <v>20/07/2026 14:12</v>
+      </c>
+      <c r="E158">
+        <v>5.24</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E158"/>
   </ignoredErrors>
 </worksheet>
 </file>